--- a/Output/Monthly Scan_14 Jul 2026.xlsx
+++ b/Output/Monthly Scan_14 Jul 2026.xlsx
@@ -509,7 +509,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>59.26</v>
+        <v>59.42</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -541,7 +541,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>49.53</v>
+        <v>48.63</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>72.54000000000001</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -605,11 +605,11 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>59.75</v>
+        <v>61.13</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -637,7 +637,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>51.32</v>
+        <v>52.36</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>51.18</v>
+        <v>50.57</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>63.33</v>
+        <v>64.28</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>67.58</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>67.14</v>
+        <v>66.81</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>61.83</v>
+        <v>62.37</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>62.65</v>
+        <v>62.04</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>52.18</v>
+        <v>51.45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -893,11 +893,11 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>61.23</v>
+        <v>59.31</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -925,7 +925,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>39.9</v>
+        <v>39.52</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>43.98</v>
+        <v>43.53</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>52.6</v>
+        <v>51.63</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>64.20999999999999</v>
+        <v>63.72</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>52.22</v>
+        <v>51.51</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1085,11 +1085,11 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>42.26</v>
+        <v>39.91</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>61.54</v>
+        <v>60.82</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>51.36</v>
+        <v>51.11</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>58.11</v>
+        <v>57.99</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>67.11</v>
+        <v>67.19</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>74.75</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>74.59</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>62.84</v>
+        <v>61.95</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>43.79</v>
+        <v>43.96</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>49.54</v>
+        <v>49.07</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>31.6</v>
+        <v>31.08</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>32.48</v>
+        <v>32.96</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>55.47</v>
+        <v>53.82</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>54.74</v>
+        <v>54.82</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>43.33</v>
+        <v>43.22</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>46.79</v>
+        <v>46.4</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>63.58</v>
+        <v>63.31</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>50</v>
+        <v>49.97</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>55.96</v>
+        <v>55.15</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>52.93</v>
+        <v>52.42</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>41.1</v>
+        <v>40.78</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>57.59</v>
+        <v>56.17</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>55.42</v>
+        <v>55.96</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>32.64</v>
+        <v>31.82</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>39.53</v>
+        <v>39.13</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>56.16</v>
+        <v>55.41</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>61.78</v>
+        <v>61.92</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>38.78</v>
+        <v>37.63</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>51.36</v>
+        <v>50.85</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>66.72</v>
+        <v>67.02</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>67.20999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>71.19</v>
+        <v>70.41</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>54.85</v>
+        <v>55.96</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>61.27</v>
+        <v>60.01</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>57.07</v>
+        <v>55.64</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>45.87</v>
+        <v>45.01</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>52.11</v>
+        <v>51.19</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>59.36</v>
+        <v>58.05</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>50.75</v>
+        <v>49.76</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>37.02</v>
+        <v>36.62</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2397,11 +2397,11 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>59.29</v>
+        <v>60.47</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -2429,7 +2429,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>55.78</v>
+        <v>56.18</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>69.73999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>63.12</v>
+        <v>62.98</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>47.39</v>
+        <v>46.94</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>31.15</v>
+        <v>30.73</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>49.67</v>
+        <v>49.39</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>57.76</v>
+        <v>57.57</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>59.63</v>
+        <v>59.42</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>62.55</v>
+        <v>62.23</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>52.79</v>
+        <v>52.41</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>62.47</v>
+        <v>61.9</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>42.99</v>
+        <v>41.04</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
-        <v>37.34</v>
+        <v>36.84</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
-        <v>49</v>
+        <v>48.66</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
-        <v>52.15</v>
+        <v>52.91</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
-        <v>52.01</v>
+        <v>52.56</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>59.16</v>
+        <v>58.36</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>43.04</v>
+        <v>42.64</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>57.05</v>
+        <v>55.79</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>54.86</v>
+        <v>53.82</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>49.94</v>
+        <v>50.69</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>68.23</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>46.54</v>
+        <v>46.66</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>52.74</v>
+        <v>51.77</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3197,11 +3197,11 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
-        <v>38.05</v>
+        <v>40.07</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>RSI &lt; 40</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -3229,7 +3229,7 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>39.34</v>
+        <v>38.82</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>58.05</v>
+        <v>57.61</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>50.63</v>
+        <v>50.02</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>55.22</v>
+        <v>54.77</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>41.24</v>
+        <v>44.19</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>51.74</v>
+        <v>51.68</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>66.36</v>
+        <v>65.31</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>60.35</v>
+        <v>60.25</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>43.53</v>
+        <v>44.89</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>55.27</v>
+        <v>54.88</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>51.91</v>
+        <v>51.15</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>57.91</v>
+        <v>56.88</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>69.81</v>
+        <v>68.78</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>51.93</v>
+        <v>52.02</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>63.52</v>
+        <v>63.22</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>51.96</v>
+        <v>51.49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
-        <v>51.53</v>
+        <v>51.57</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
-        <v>62.31</v>
+        <v>64.27</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
-        <v>48.99</v>
+        <v>48.91</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
-        <v>67</v>
+        <v>67.88</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
-        <v>52.8</v>
+        <v>52.05</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>50.67</v>
+        <v>51.66</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
-        <v>50.33</v>
+        <v>49.58</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
-        <v>42.5</v>
+        <v>41.87</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>61.18</v>
+        <v>60.7</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>58.74</v>
+        <v>57.9</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>67.8</v>
+        <v>65.41</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>49.14</v>
+        <v>49.24</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
-        <v>59.03</v>
+        <v>58.55</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="n">
-        <v>53.48</v>
+        <v>52.04</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
-        <v>69.76000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>54.69</v>
+        <v>53.17</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>56.81</v>
+        <v>55.39</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>64.44</v>
+        <v>64.75</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>67</v>
+        <v>67.13</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>48.87</v>
+        <v>48.46</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>76.45</v>
+        <v>75.78</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>60.7</v>
+        <v>60.56</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>51.07</v>
+        <v>50.25</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>58.02</v>
+        <v>58.64</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>71.78</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>52.88</v>
+        <v>53.48</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>51.29</v>
+        <v>49.66</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>54.93</v>
+        <v>53.38</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>63.65</v>
+        <v>63.52</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
-        <v>53.01</v>
+        <v>53.27</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
-        <v>70.77</v>
+        <v>69.73</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>70.40000000000001</v>
+        <v>69.37</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>80.31999999999999</v>
+        <v>80.36</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
-        <v>62.34</v>
+        <v>63.05</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
-        <v>59.04</v>
+        <v>58.35</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="n">
-        <v>59.77</v>
+        <v>59.9</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>52.69</v>
+        <v>52.54</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>38.95</v>
+        <v>37.4</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
-        <v>58.09</v>
+        <v>57.08</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>79.81999999999999</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>75.63</v>
+        <v>75.69</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>41.37</v>
+        <v>42.53</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>65.12</v>
+        <v>64.16</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>62.62</v>
+        <v>64.17</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>47.2</v>
+        <v>47.38</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>64.72</v>
+        <v>65.41</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>38.93</v>
+        <v>39.42</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>56.59</v>
+        <v>55.54</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>68.38</v>
+        <v>68.5</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>60.47</v>
+        <v>60.1</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>66.59999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>54.99</v>
+        <v>53.62</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>51.26</v>
+        <v>51.93</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>66.75</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>56.33</v>
+        <v>54.79</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>52.7</v>
+        <v>51.86</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>58.03</v>
+        <v>57.43</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>55.29</v>
+        <v>54.78</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -5629,11 +5629,11 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>60.91</v>
+        <v>59.78</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -5661,7 +5661,7 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>72.51000000000001</v>
+        <v>72.02</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>56.88</v>
+        <v>55.97</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
-        <v>54.14</v>
+        <v>54.56</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="n">
-        <v>58.69</v>
+        <v>59.56</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="n">
-        <v>49.14</v>
+        <v>48.2</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="n">
-        <v>50.81</v>
+        <v>51.12</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="n">
-        <v>49.19</v>
+        <v>48.83</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="n">
-        <v>60.68</v>
+        <v>60.78</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
-        <v>49.84</v>
+        <v>49.94</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
-        <v>45.95</v>
+        <v>45.71</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -5981,11 +5981,11 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
-        <v>40.76</v>
+        <v>39.94</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -6013,7 +6013,7 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
-        <v>48.95</v>
+        <v>47.79</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
-        <v>56.49</v>
+        <v>55.76</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>68.8</v>
+        <v>68.3</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>60.98</v>
+        <v>60.96</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>49.99</v>
+        <v>50.02</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>52.84</v>
+        <v>51.54</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>59.2</v>
+        <v>58.92</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -6237,11 +6237,11 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>58.31</v>
+        <v>62</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -6269,7 +6269,7 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>69.87</v>
+        <v>69.58</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>56.06</v>
+        <v>55.63</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>48.92</v>
+        <v>48.33</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>49.4</v>
+        <v>49.26</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>64.45</v>
+        <v>63.81</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>57.38</v>
+        <v>56.64</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>69.91</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>60.99</v>
+        <v>61.33</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="n">
-        <v>48.7</v>
+        <v>47.79</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="n">
-        <v>50.12</v>
+        <v>49.73</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="n">
-        <v>52.33</v>
+        <v>53.03</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="n">
-        <v>57.2</v>
+        <v>57.27</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="n">
-        <v>44.09</v>
+        <v>43.27</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="n">
-        <v>61.66</v>
+        <v>61.38</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="n">
-        <v>56.07</v>
+        <v>55.42</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="n">
-        <v>35.77</v>
+        <v>35.27</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="n">
-        <v>51.65</v>
+        <v>50.85</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="n">
-        <v>55.87</v>
+        <v>55.15</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="n">
-        <v>61.64</v>
+        <v>60.66</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="n">
-        <v>36.97</v>
+        <v>36.85</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="n">
-        <v>41.75</v>
+        <v>41.39</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="n">
-        <v>48.71</v>
+        <v>47.67</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="n">
-        <v>51.53</v>
+        <v>50.9</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>51.27</v>
+        <v>50.67</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -7037,11 +7037,11 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>59.35</v>
+        <v>60.4</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -7246,7 +7246,11 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -7272,11 +7276,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -8592,11 +8592,7 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -9936,11 +9932,7 @@
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
@@ -10234,11 +10226,7 @@
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
@@ -11324,11 +11312,7 @@
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
@@ -12206,7 +12190,11 @@
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
@@ -18958,7 +18946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19104,7 +19092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -19123,19 +19111,19 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AANGELONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGLENMARK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -19149,14 +19137,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGLENMARK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -19175,7 +19163,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTHERSON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AASHOKLEY</t>
         </is>
       </c>
     </row>
@@ -19260,7 +19248,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -19279,19 +19267,19 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APNB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALICHSGFIN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -19305,14 +19293,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJFINSV</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMARUTI</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -19331,14 +19319,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOCHINSHIP</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABDL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -19357,19 +19345,19 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLYCAB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APNB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -19383,14 +19371,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARECLTD</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -19409,14 +19397,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOCHINSHIP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -19435,19 +19423,19 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACIPLA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJHLDNG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -19461,19 +19449,19 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMANAPPURAM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLYCAB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -19487,14 +19475,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMFSL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -19513,19 +19501,19 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMANAPPURAM</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -19539,14 +19527,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATRENT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -19565,14 +19553,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKEI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATRENT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -19591,19 +19579,19 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKOTAKBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKEI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -19617,19 +19605,19 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIGI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKOTAKBANK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -19643,19 +19631,19 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANBCC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIGI</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -19669,14 +19657,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAUKRI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANBCC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -19694,6 +19682,84 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AYESBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APETRONET</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAUKRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHINDPETRO</t>
         </is>
@@ -28812,7 +28878,11 @@
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Probable Bearish Reversal</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
@@ -31208,7 +31278,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -31298,7 +31368,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -32108,7 +32178,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bullish Reversal Watch</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -33248,7 +33318,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -33428,7 +33498,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -33998,7 +34068,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -34358,7 +34428,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Bullish Reversal Watch</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -34748,7 +34818,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -36488,7 +36558,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
